--- a/策划/excel/15_FightEvent.xlsx
+++ b/策划/excel/15_FightEvent.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27765" windowHeight="9540"/>
+    <workbookView windowWidth="27315" windowHeight="10470"/>
   </bookViews>
   <sheets>
     <sheet name="15_FightEvent" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="212">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -70,10 +70,604 @@
     <t>client</t>
   </si>
   <si>
-    <t>追逐太阳的斯库尔</t>
-  </si>
-  <si>
-    <t>在约顿海姆的极寒荒原上，巨狼斯库尔正奋力追逐高悬天空的太阳。它穿过冰川与断崖，永不停歇，只为将光明吞噬，迎来终焉之时。它的身影掠过雪原，察觉到了你的到来。</t>
+    <t>遭遇劫掠者刺客</t>
+  </si>
+  <si>
+    <t>劫掠者刺客挡住了去路。它可能使用致命一击。</t>
+  </si>
+  <si>
+    <t>遭遇劫掠者斧手</t>
+  </si>
+  <si>
+    <t>劫掠者斧手挡住了去路。它可能使用挥砍一式、挥砍二式、重斧横扫。</t>
+  </si>
+  <si>
+    <t>遭遇盛碗虫（丝）</t>
+  </si>
+  <si>
+    <t>盛碗虫（丝）挡住了去路。它可能使用毒液喷吐、乱击。</t>
+  </si>
+  <si>
+    <t>遭遇旧日雕像</t>
+  </si>
+  <si>
+    <t>旧日雕像挡住了去路。它可能使用沉睡、苏醒、连环斩击。</t>
+  </si>
+  <si>
+    <t>遭遇多尼斯异鸟</t>
+  </si>
+  <si>
+    <t>多尼斯异鸟挡住了去路。它可能使用俯冲、啄击。</t>
+  </si>
+  <si>
+    <t>遭遇拳击构装体</t>
+  </si>
+  <si>
+    <t>拳击构装体挡住了去路。它可能使用准备就绪、快速拳、重拳。</t>
+  </si>
+  <si>
+    <t>遭遇下水道蚌</t>
+  </si>
+  <si>
+    <t>下水道蚌挡住了去路。它可能使用水流喷射、加压。</t>
+  </si>
+  <si>
+    <t>遭遇墨影幻灵</t>
+  </si>
+  <si>
+    <t>墨影幻灵挡住了去路。它可能使用墨迹、墨枪、肢解、蓄势。</t>
+  </si>
+  <si>
+    <t>遭遇巨斧机器人</t>
+  </si>
+  <si>
+    <t>巨斧机器人挡住了去路。它可能使用启动、左右连击、铁锤上勾拳。</t>
+  </si>
+  <si>
+    <t>遭遇永世沙漏</t>
+  </si>
+  <si>
+    <t>永世沙漏挡住了去路。它可能使用退潮、眼部激光、强度增长。</t>
+  </si>
+  <si>
+    <t>遭遇长牙之眼</t>
+  </si>
+  <si>
+    <t>长牙之眼挡住了去路。它可能使用干扰。</t>
+  </si>
+  <si>
+    <t>遭遇枝条史莱姆（小）</t>
+  </si>
+  <si>
+    <t>枝条史莱姆（小）挡住了去路。它可能使用冲撞。</t>
+  </si>
+  <si>
+    <t>遭遇毒气炸弹</t>
+  </si>
+  <si>
+    <t>毒气炸弹挡住了去路。它可能使用爆炸。</t>
+  </si>
+  <si>
+    <t>遭遇鬼祟地精</t>
+  </si>
+  <si>
+    <t>鬼祟地精挡住了去路。它可能使用冲撞。</t>
+  </si>
+  <si>
+    <t>遭遇小墨灵</t>
+  </si>
+  <si>
+    <t>小墨灵挡住了去路。它可能使用刺拳、旋风连击、穿透凝视。</t>
+  </si>
+  <si>
+    <t>遭遇树叶史莱姆（小）</t>
+  </si>
+  <si>
+    <t>树叶史莱姆（小）挡住了去路。它可能使用冲撞、黏浆。</t>
+  </si>
+  <si>
+    <t>遭遇肥胖地精</t>
+  </si>
+  <si>
+    <t>肥胖地精挡住了去路。它可能使用逃跑。</t>
+  </si>
+  <si>
+    <t>遭遇双尾鼠</t>
+  </si>
+  <si>
+    <t>双尾鼠挡住了去路。它可能使用抓挠、疫病啃咬、尖啸、呼叫援兵。</t>
+  </si>
+  <si>
+    <t>遭遇蠕动虫</t>
+  </si>
+  <si>
+    <t>蠕动虫挡住了去路。它可能使用恶毒啃咬、蠕动。</t>
+  </si>
+  <si>
+    <t>遭遇粉碎者</t>
+  </si>
+  <si>
+    <t>粉碎者挡住了去路。它可能使用乱击、膨胀打击、虫刺、适应、防御打击。</t>
+  </si>
+  <si>
+    <t>遭遇红宝石劫掠者（弩手）</t>
+  </si>
+  <si>
+    <t>红宝石劫掠者（弩手）挡住了去路。它可能使用装填、射击。</t>
+  </si>
+  <si>
+    <t>遭遇幼虫</t>
+  </si>
+  <si>
+    <t>幼虫挡住了去路。它可能使用轻咬。</t>
+  </si>
+  <si>
+    <t>遭遇护卫机器人</t>
+  </si>
+  <si>
+    <t>护卫机器人挡住了去路。它可能使用守护。</t>
+  </si>
+  <si>
+    <t>遭遇幻惧灵</t>
+  </si>
+  <si>
+    <t>幻惧灵挡住了去路。它可能使用猛击。</t>
+  </si>
+  <si>
+    <t>遭遇红宝石劫掠者（追踪者）</t>
+  </si>
+  <si>
+    <t>红宝石劫掠者（追踪者）挡住了去路。它可能使用追踪、猎犬突袭。</t>
+  </si>
+  <si>
+    <t>遭遇蝌蚪</t>
+  </si>
+  <si>
+    <t>蝌蚪挡住了去路。它可能使用生长尖刺、尖刺喷吐、旋转。</t>
+  </si>
+  <si>
+    <t>遭遇噪音机器人</t>
+  </si>
+  <si>
+    <t>噪音机器人挡住了去路。它可能使用噪音。</t>
+  </si>
+  <si>
+    <t>遭遇刺击机器人</t>
+  </si>
+  <si>
+    <t>刺击机器人挡住了去路。它可能使用刺击。</t>
+  </si>
+  <si>
+    <t>遭遇电击机器人</t>
+  </si>
+  <si>
+    <t>电击机器人挡住了去路。它可能使用电击、高压电。</t>
+  </si>
+  <si>
+    <t>遭遇灵魂鱼</t>
+  </si>
+  <si>
+    <t>灵魂鱼挡住了去路。它可能使用召唤低语、排气、凝视、隐没、尖叫。</t>
+  </si>
+  <si>
+    <t>遭遇外骨骼虫</t>
+  </si>
+  <si>
+    <t>外骨骼虫挡住了去路。它可能使用疾行、颚击、狂怒。</t>
+  </si>
+  <si>
+    <t>遭遇尸蛞蝓</t>
+  </si>
+  <si>
+    <t>尸蛞蝓挡住了去路。它可能使用鞭打、猛扑、黏液喷吐。</t>
+  </si>
+  <si>
+    <t>遭遇枝条史莱姆（中）</t>
+  </si>
+  <si>
+    <t>枝条史莱姆（中）挡住了去路。它可能使用黏液弹、黏团弹。</t>
+  </si>
+  <si>
+    <t>遭遇幻影园丁</t>
+  </si>
+  <si>
+    <t>幻影园丁挡住了去路。它可能使用啃咬、鞭击、链锤乱击、膨大。</t>
+  </si>
+  <si>
+    <t>遭遇红宝石劫掠者（蛮兵）</t>
+  </si>
+  <si>
+    <t>红宝石劫掠者（蛮兵）挡住了去路。它可能使用殴打、咆哮。</t>
+  </si>
+  <si>
+    <t>遭遇噬咬卷轴</t>
+  </si>
+  <si>
+    <t>噬咬卷轴挡住了去路。它可能使用猛咬、咀嚼、增生利齿。</t>
+  </si>
+  <si>
+    <t>遭遇咬合杰克果</t>
+  </si>
+  <si>
+    <t>咬合杰克果挡住了去路。它可能使用能量球。</t>
+  </si>
+  <si>
+    <t>遭遇树叶史莱姆（中）</t>
+  </si>
+  <si>
+    <t>树叶史莱姆（中）挡住了去路。它可能使用黏液弹、黏团弹。</t>
+  </si>
+  <si>
+    <t>遭遇盛碗虫（蜜）</t>
+  </si>
+  <si>
+    <t>盛碗虫（蜜）挡住了去路。它可能使用乱击、强化。</t>
+  </si>
+  <si>
+    <t>遭遇拉加维林族母</t>
+  </si>
+  <si>
+    <t>拉加维林族母挡住了去路。它可能使用斩击、开膛、斩击二式、灵魂虹吸。</t>
+  </si>
+  <si>
+    <t>遭遇淤泥纺织者</t>
+  </si>
+  <si>
+    <t>淤泥纺织者挡住了去路。它可能使用喷油、猛击、暴怒。</t>
+  </si>
+  <si>
+    <t>遭遇钙化教徒</t>
+  </si>
+  <si>
+    <t>钙化教徒挡住了去路。它可能使用吟唱、暗影打击。</t>
+  </si>
+  <si>
+    <t>遭遇缩小甲虫</t>
+  </si>
+  <si>
+    <t>缩小甲虫挡住了去路。它可能使用缩小术、猛咬、跺击。</t>
+  </si>
+  <si>
+    <t>遭遇炮塔操作员</t>
+  </si>
+  <si>
+    <t>炮塔操作员挡住了去路。它可能使用倾泻火力、装填。</t>
+  </si>
+  <si>
+    <t>遭遇千足虫</t>
+  </si>
+  <si>
+    <t>千足虫挡住了去路。它可能使用扭动攻击、壮大、紧缚。</t>
+  </si>
+  <si>
+    <t>遭遇啃咬虫</t>
+  </si>
+  <si>
+    <t>啃咬虫挡住了去路。它可能使用头槌、切割、嘶鸣。</t>
+  </si>
+  <si>
+    <t>遭遇海朋克</t>
+  </si>
+  <si>
+    <t>海朋克挡住了去路。它可能使用海潮踢、回旋踢、气泡嗝。</t>
+  </si>
+  <si>
+    <t>遭遇盛碗虫（岩）</t>
+  </si>
+  <si>
+    <t>盛碗虫（岩）挡住了去路。它可能使用头槌、眩晕。</t>
+  </si>
+  <si>
+    <t>遭遇飞菇</t>
+  </si>
+  <si>
+    <t>飞菇挡住了去路。它可能使用脆弱孢子、重击、易伤孢子。</t>
+  </si>
+  <si>
+    <t>遭遇瀑布巨人</t>
+  </si>
+  <si>
+    <t>瀑布巨人挡住了去路。它可能使用加压、跺击、猛撞、虹吸、高压水枪、增压。</t>
+  </si>
+  <si>
+    <t>遭遇地精佣兵</t>
+  </si>
+  <si>
+    <t>地精佣兵挡住了去路。它可能使用交出来、双重猛击、嘿嘿。</t>
+  </si>
+  <si>
+    <t>遭遇潮湿教徒</t>
+  </si>
+  <si>
+    <t>潮湿教徒挡住了去路。它可能使用吟唱、暗影打击。</t>
+  </si>
+  <si>
+    <t>遭遇化石潜猎者</t>
+  </si>
+  <si>
+    <t>化石潜猎者挡住了去路。它可能使用咬住、冲撞、鞭击。</t>
+  </si>
+  <si>
+    <t>遭遇游蛇绞杀者</t>
+  </si>
+  <si>
+    <t>游蛇绞杀者挡住了去路。它可能使用紧缚、抽打、鞭击。</t>
+  </si>
+  <si>
+    <t>遭遇绒毛蠕虫</t>
+  </si>
+  <si>
+    <t>绒毛蠕虫挡住了去路。它可能使用酸液黏浆、吸气。</t>
+  </si>
+  <si>
+    <t>遭遇活体盾牌</t>
+  </si>
+  <si>
+    <t>活体盾牌挡住了去路。它可能使用盾击、重击。</t>
+  </si>
+  <si>
+    <t>遭遇眷族追随者</t>
+  </si>
+  <si>
+    <t>眷族追随者挡住了去路。它可能使用迅捷斩击、回旋斩、力量之舞。</t>
+  </si>
+  <si>
+    <t>遭遇巨口兽</t>
+  </si>
+  <si>
+    <t>巨口兽挡住了去路。它可能使用钳击、尖啸。</t>
+  </si>
+  <si>
+    <t>遭遇螨虫</t>
+  </si>
+  <si>
+    <t>螨虫挡住了去路。它可能使用毒液、啃咬、吸吮。</t>
+  </si>
+  <si>
+    <t>遭遇仪式巨兽</t>
+  </si>
+  <si>
+    <t>仪式巨兽挡住了去路。它可能使用践踏、巨兽咆哮、跺击、碾压、犁地。</t>
+  </si>
+  <si>
+    <t>遭遇蛙寄生虫</t>
+  </si>
+  <si>
+    <t>蛙寄生虫挡住了去路。它可能使用感染、鞭击。</t>
+  </si>
+  <si>
+    <t>遭遇藤蔓蹒跚者</t>
+  </si>
+  <si>
+    <t>藤蔓蹒跚者挡住了去路。它可能使用缠绕藤蔓、横扫、猛咬。</t>
+  </si>
+  <si>
+    <t>遭遇幽灵船</t>
+  </si>
+  <si>
+    <t>幽灵船挡住了去路。它可能使用全速冲撞、缠魂、横扫、跺击。</t>
+  </si>
+  <si>
+    <t>遭遇立方构装体</t>
+  </si>
+  <si>
+    <t>立方构装体挡住了去路。它可能使用蓄能、连发冲击、喷射冲击、下潜。</t>
+  </si>
+  <si>
+    <t>遭遇巨颚兽</t>
+  </si>
+  <si>
+    <t>巨颚兽挡住了去路。它可能使用爪击、咆哮、撕扯。</t>
+  </si>
+  <si>
+    <t>遭遇雾魔</t>
+  </si>
+  <si>
+    <t>雾魔挡住了去路。它可能使用幻象、横扫、头槌。</t>
+  </si>
+  <si>
+    <t>遭遇潜伏群落</t>
+  </si>
+  <si>
+    <t>潜伏群落挡住了去路。它可能使用重击、疾速冲击、惯性、巨蟹冲击。</t>
+  </si>
+  <si>
+    <t>遭遇窃贼跳虫</t>
+  </si>
+  <si>
+    <t>窃贼跳虫挡住了去路。它可能使用偷窃、振翅、帽子戏法、夺取、逃离。</t>
+  </si>
+  <si>
+    <t>遭遇活体迷雾</t>
+  </si>
+  <si>
+    <t>活体迷雾挡住了去路。它可能使用强化毒雾、膨胀、超级毒雾爆发。</t>
+  </si>
+  <si>
+    <t>遭遇贪得无厌者</t>
+  </si>
+  <si>
+    <t>贪得无厌者挡住了去路。它可能使用液化地面、乱击、突进啃咬、垂涎。</t>
+  </si>
+  <si>
+    <t>遭遇魔法骑士</t>
+  </si>
+  <si>
+    <t>魔法骑士挡住了去路。它可能使用能量盾、压制、长枪突刺、准备、魔法炸弹。</t>
+  </si>
+  <si>
+    <t>遭遇沉睡甲虫</t>
+  </si>
+  <si>
+    <t>沉睡甲虫挡住了去路。它可能使用沉睡、滚动突击。</t>
+  </si>
+  <si>
+    <t>遭遇掘地兽</t>
+  </si>
+  <si>
+    <t>掘地兽挡住了去路。它可能使用啃咬、潜地、地底突袭。</t>
+  </si>
+  <si>
+    <t>遭遇幽魂骑士</t>
+  </si>
+  <si>
+    <t>幽魂骑士挡住了去路。它可能使用诅咒、灵魂斩击、灵魂烈焰。</t>
+  </si>
+  <si>
+    <t>遭遇迷失者</t>
+  </si>
+  <si>
+    <t>迷失者挡住了去路。它可能使用虚弱迷雾、眼部激光。</t>
+  </si>
+  <si>
+    <t>遭遇链锤骑士</t>
+  </si>
+  <si>
+    <t>链锤骑士挡住了去路。它可能使用猛撞、战歌、链锤乱击。</t>
+  </si>
+  <si>
+    <t>遭遇遗忘者</t>
+  </si>
+  <si>
+    <t>遗忘者挡住了去路。它可能使用瘴气、恐惧。</t>
+  </si>
+  <si>
+    <t>遭遇棘刺蟾蜍</t>
+  </si>
+  <si>
+    <t>棘刺蟾蜍挡住了去路。它可能使用凸出尖刺、尖刺爆发、舌鞭。</t>
+  </si>
+  <si>
+    <t>遭遇猎杀者</t>
+  </si>
+  <si>
+    <t>猎杀者挡住了去路。它可能使用软化黏液、啃咬、穿刺。</t>
+  </si>
+  <si>
+    <t>遭遇知识恶魔</t>
+  </si>
+  <si>
+    <t>知识恶魔挡住了去路。它可能使用知识诅咒、拍击、知识洪流、沉思。</t>
+  </si>
+  <si>
+    <t>遭遇晦影者</t>
+  </si>
+  <si>
+    <t>晦影者挡住了去路。它可能使用幻象、穿透凝视、哀嚎、硬化打击。</t>
+  </si>
+  <si>
+    <t>遭遇产卵飞虫</t>
+  </si>
+  <si>
+    <t>产卵飞虫挡住了去路。它可能使用产卵、重击、软化打击、营养糊。</t>
+  </si>
+  <si>
+    <t>遭遇虱虫始祖</t>
+  </si>
+  <si>
+    <t>虱虫始祖挡住了去路。它可能使用蛛网炮、蜷缩成长、扑击。</t>
+  </si>
+  <si>
+    <t>遭遇恐惧鳗鱼</t>
+  </si>
+  <si>
+    <t>恐惧鳗鱼挡住了去路。它可能使用撞击、乱击、恐吓。</t>
+  </si>
+  <si>
+    <t>遭遇御虫师</t>
+  </si>
+  <si>
+    <t>御虫师挡住了去路。它可能使用蜂群、长枪突刺、信息素喷吐。</t>
+  </si>
+  <si>
+    <t>遭遇球头怪</t>
+  </si>
+  <si>
+    <t>球头怪挡住了去路。它可能使用电击掌、雷霆打击、电流爆发。</t>
+  </si>
+  <si>
+    <t>遭遇制造者</t>
+  </si>
+  <si>
+    <t>制造者挡住了去路。它可能使用制造、制造打击、瓦解。</t>
+  </si>
+  <si>
+    <t>遭遇虔诚雕塑师</t>
+  </si>
+  <si>
+    <t>虔诚雕塑师挡住了去路。它可能使用禁忌咒语、狂野打击。</t>
+  </si>
+  <si>
+    <t>遭遇伪装商人</t>
+  </si>
+  <si>
+    <t>伪装商人挡住了去路。它可能使用横扫、喷射硬币、投掷遗物、狂怒。</t>
+  </si>
+  <si>
+    <t>遭遇女王</t>
+  </si>
+  <si>
+    <t>女王挡住了去路。它可能使用傀儡丝线、你属于我、为我燃烧、斩下你的头、处决、狂怒。</t>
+  </si>
+  <si>
+    <t>遭遇火箭</t>
+  </si>
+  <si>
+    <t>火箭挡住了去路。它可能使用锁定准星、精准光束、蓄能、激光、重新充能。</t>
+  </si>
+  <si>
+    <t>遭遇眷族祭司</t>
+  </si>
+  <si>
+    <t>眷族祭司挡住了去路。它可能使用脆弱法球、虚弱法球、光束、仪式。</t>
+  </si>
+  <si>
+    <t>遭遇青蛙骑士</t>
+  </si>
+  <si>
+    <t>青蛙骑士挡住了去路。它可能使用舌鞭、讨伐邪恶、为了女王、甲虫冲锋。</t>
+  </si>
+  <si>
+    <t>遭遇火炬头融合体</t>
+  </si>
+  <si>
+    <t>火炬头融合体挡住了去路。它可能使用冲撞、灵魂光束、虚弱冲撞。</t>
+  </si>
+  <si>
+    <t>遭遇寄生棱晶</t>
+  </si>
+  <si>
+    <t>寄生棱晶挡住了去路。它可能使用刺拳、辐射、旋风连击、脉动。</t>
+  </si>
+  <si>
+    <t>遭遇猫头鹰裁判官</t>
+  </si>
+  <si>
+    <t>猫头鹰裁判官挡住了去路。它可能使用裁判审视、连环啄击、审判之翼、判决。</t>
+  </si>
+  <si>
+    <t>遭遇灵魂枢纽</t>
+  </si>
+  <si>
+    <t>灵魂枢纽挡住了去路。它可能使用灵魂灼烧、漩涡、汲取生命。</t>
+  </si>
+  <si>
+    <t>遭遇黏液狂战士</t>
+  </si>
+  <si>
+    <t>黏液狂战士挡住了去路。它可能使用喷吐脓液、狂怒连打、吸血拥抱、窒息。</t>
+  </si>
+  <si>
+    <t>遭遇机甲骑士</t>
+  </si>
+  <si>
+    <t>机甲骑士挡住了去路。它可能使用冲锋、火焰喷射、蓄力、沉重劈砍。</t>
+  </si>
+  <si>
+    <t>遭遇造门者</t>
+  </si>
+  <si>
+    <t>造门者挡住了去路。它可能使用光束、退回门内。</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1602,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="25.375" customWidth="1"/>
@@ -1091,7 +1685,7 @@
         <v>150001</v>
       </c>
       <c r="B6" s="1">
-        <v>50001</v>
+        <v>50002</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -1105,13 +1699,13 @@
         <v>150002</v>
       </c>
       <c r="B7" s="1">
-        <v>50001</v>
+        <v>50003</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:4">
@@ -1119,13 +1713,13 @@
         <v>150003</v>
       </c>
       <c r="B8" s="1">
-        <v>50001</v>
+        <v>50004</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:4">
@@ -1133,13 +1727,13 @@
         <v>150004</v>
       </c>
       <c r="B9" s="1">
-        <v>50001</v>
+        <v>50005</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:4">
@@ -1147,13 +1741,13 @@
         <v>150005</v>
       </c>
       <c r="B10" s="1">
-        <v>50001</v>
+        <v>50006</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:4">
@@ -1161,13 +1755,13 @@
         <v>150006</v>
       </c>
       <c r="B11" s="1">
-        <v>50001</v>
+        <v>50007</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:4">
@@ -1175,13 +1769,13 @@
         <v>150007</v>
       </c>
       <c r="B12" s="1">
-        <v>50001</v>
+        <v>50008</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:4">
@@ -1189,13 +1783,13 @@
         <v>150008</v>
       </c>
       <c r="B13" s="1">
-        <v>50001</v>
+        <v>50009</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:4">
@@ -1203,13 +1797,13 @@
         <v>150009</v>
       </c>
       <c r="B14" s="1">
-        <v>50001</v>
+        <v>50010</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:4">
@@ -1217,258 +1811,1274 @@
         <v>150010</v>
       </c>
       <c r="B15" s="1">
-        <v>50001</v>
+        <v>50011</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:4">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:2">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:2">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:2">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:2">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:2">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:2">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:2">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:2">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:2">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:2">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:2">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:2">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:2">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:2">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:2">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:2">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:2">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:2">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:2">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:2">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:2">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:2">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:2">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:2">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:2">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:2">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:2">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:2">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:2">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:2">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:2">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:2">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:2">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:2">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-    </row>
-    <row r="54" customHeight="1" spans="1:2">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-    </row>
-    <row r="55" customHeight="1" spans="1:2">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-    </row>
-    <row r="56" customHeight="1" spans="1:2">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-    </row>
-    <row r="57" customHeight="1" spans="1:2">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-    </row>
-    <row r="58" customHeight="1" spans="1:2">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-    </row>
-    <row r="59" customHeight="1" spans="1:2">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-    </row>
-    <row r="60" customHeight="1" spans="1:2">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-    </row>
-    <row r="61" customHeight="1" spans="1:2">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-    </row>
-    <row r="62" customHeight="1" spans="1:2">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-    </row>
-    <row r="63" customHeight="1" spans="1:2">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-    </row>
-    <row r="64" customHeight="1" spans="1:2">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-    </row>
-    <row r="65" customHeight="1" spans="1:2">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-    </row>
-    <row r="66" customHeight="1" spans="1:2">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-    </row>
-    <row r="67" customHeight="1" spans="1:2">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-    </row>
-    <row r="68" customHeight="1" spans="1:2">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-    </row>
-    <row r="69" customHeight="1" spans="1:2">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-    </row>
-    <row r="70" customHeight="1" spans="1:2">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-    </row>
-    <row r="71" customHeight="1" spans="1:2">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-    </row>
-    <row r="72" customHeight="1" spans="1:2">
-      <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
-    </row>
-    <row r="73" customHeight="1" spans="1:2">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
-    </row>
-    <row r="74" customHeight="1" spans="1:2">
-      <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
-    </row>
-    <row r="75" customHeight="1" spans="1:2">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-    </row>
-    <row r="76" customHeight="1" spans="1:2">
-      <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
+      <c r="A16" s="1">
+        <v>150011</v>
+      </c>
+      <c r="B16" s="1">
+        <v>50012</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:4">
+      <c r="A17" s="1">
+        <v>150012</v>
+      </c>
+      <c r="B17" s="1">
+        <v>50013</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:4">
+      <c r="A18" s="1">
+        <v>150013</v>
+      </c>
+      <c r="B18" s="1">
+        <v>50014</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:4">
+      <c r="A19" s="1">
+        <v>150014</v>
+      </c>
+      <c r="B19" s="1">
+        <v>50015</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:4">
+      <c r="A20" s="1">
+        <v>150015</v>
+      </c>
+      <c r="B20" s="1">
+        <v>50016</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:4">
+      <c r="A21" s="1">
+        <v>150016</v>
+      </c>
+      <c r="B21" s="1">
+        <v>50017</v>
+      </c>
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:4">
+      <c r="A22" s="1">
+        <v>150017</v>
+      </c>
+      <c r="B22" s="1">
+        <v>50018</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:4">
+      <c r="A23" s="1">
+        <v>150018</v>
+      </c>
+      <c r="B23" s="1">
+        <v>50019</v>
+      </c>
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:4">
+      <c r="A24" s="1">
+        <v>150019</v>
+      </c>
+      <c r="B24" s="1">
+        <v>50020</v>
+      </c>
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:4">
+      <c r="A25" s="1">
+        <v>150020</v>
+      </c>
+      <c r="B25" s="1">
+        <v>50021</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:4">
+      <c r="A26" s="1">
+        <v>150021</v>
+      </c>
+      <c r="B26" s="1">
+        <v>50022</v>
+      </c>
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:4">
+      <c r="A27" s="1">
+        <v>150022</v>
+      </c>
+      <c r="B27" s="1">
+        <v>50023</v>
+      </c>
+      <c r="C27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:4">
+      <c r="A28" s="1">
+        <v>150023</v>
+      </c>
+      <c r="B28" s="1">
+        <v>50024</v>
+      </c>
+      <c r="C28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:4">
+      <c r="A29" s="1">
+        <v>150024</v>
+      </c>
+      <c r="B29" s="1">
+        <v>50025</v>
+      </c>
+      <c r="C29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:4">
+      <c r="A30" s="1">
+        <v>150025</v>
+      </c>
+      <c r="B30" s="1">
+        <v>50026</v>
+      </c>
+      <c r="C30" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:4">
+      <c r="A31" s="1">
+        <v>150026</v>
+      </c>
+      <c r="B31" s="1">
+        <v>50027</v>
+      </c>
+      <c r="C31" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:4">
+      <c r="A32" s="1">
+        <v>150027</v>
+      </c>
+      <c r="B32" s="1">
+        <v>50028</v>
+      </c>
+      <c r="C32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:4">
+      <c r="A33" s="1">
+        <v>150028</v>
+      </c>
+      <c r="B33" s="1">
+        <v>50029</v>
+      </c>
+      <c r="C33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:4">
+      <c r="A34" s="1">
+        <v>150029</v>
+      </c>
+      <c r="B34" s="1">
+        <v>50030</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:4">
+      <c r="A35" s="1">
+        <v>150030</v>
+      </c>
+      <c r="B35" s="1">
+        <v>50031</v>
+      </c>
+      <c r="C35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:4">
+      <c r="A36" s="1">
+        <v>150031</v>
+      </c>
+      <c r="B36" s="1">
+        <v>50032</v>
+      </c>
+      <c r="C36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:4">
+      <c r="A37" s="1">
+        <v>150032</v>
+      </c>
+      <c r="B37" s="1">
+        <v>50033</v>
+      </c>
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:4">
+      <c r="A38" s="1">
+        <v>150033</v>
+      </c>
+      <c r="B38" s="1">
+        <v>50034</v>
+      </c>
+      <c r="C38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:4">
+      <c r="A39" s="1">
+        <v>150034</v>
+      </c>
+      <c r="B39" s="1">
+        <v>50035</v>
+      </c>
+      <c r="C39" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:4">
+      <c r="A40" s="1">
+        <v>150035</v>
+      </c>
+      <c r="B40" s="1">
+        <v>50036</v>
+      </c>
+      <c r="C40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:4">
+      <c r="A41" s="1">
+        <v>150036</v>
+      </c>
+      <c r="B41" s="1">
+        <v>50037</v>
+      </c>
+      <c r="C41" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:4">
+      <c r="A42" s="1">
+        <v>150037</v>
+      </c>
+      <c r="B42" s="1">
+        <v>50038</v>
+      </c>
+      <c r="C42" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:4">
+      <c r="A43" s="1">
+        <v>150038</v>
+      </c>
+      <c r="B43" s="1">
+        <v>50039</v>
+      </c>
+      <c r="C43" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:4">
+      <c r="A44" s="1">
+        <v>150039</v>
+      </c>
+      <c r="B44" s="1">
+        <v>50040</v>
+      </c>
+      <c r="C44" t="s">
+        <v>88</v>
+      </c>
+      <c r="D44" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:4">
+      <c r="A45" s="1">
+        <v>150040</v>
+      </c>
+      <c r="B45" s="1">
+        <v>50041</v>
+      </c>
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:4">
+      <c r="A46" s="1">
+        <v>150041</v>
+      </c>
+      <c r="B46" s="1">
+        <v>50042</v>
+      </c>
+      <c r="C46" t="s">
+        <v>92</v>
+      </c>
+      <c r="D46" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:4">
+      <c r="A47" s="1">
+        <v>150042</v>
+      </c>
+      <c r="B47" s="1">
+        <v>50043</v>
+      </c>
+      <c r="C47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:4">
+      <c r="A48" s="1">
+        <v>150043</v>
+      </c>
+      <c r="B48" s="1">
+        <v>50044</v>
+      </c>
+      <c r="C48" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:4">
+      <c r="A49" s="1">
+        <v>150044</v>
+      </c>
+      <c r="B49" s="1">
+        <v>50045</v>
+      </c>
+      <c r="C49" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:4">
+      <c r="A50" s="1">
+        <v>150045</v>
+      </c>
+      <c r="B50" s="1">
+        <v>50046</v>
+      </c>
+      <c r="C50" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:4">
+      <c r="A51" s="1">
+        <v>150046</v>
+      </c>
+      <c r="B51" s="1">
+        <v>50047</v>
+      </c>
+      <c r="C51" t="s">
+        <v>102</v>
+      </c>
+      <c r="D51" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:4">
+      <c r="A52" s="1">
+        <v>150047</v>
+      </c>
+      <c r="B52" s="1">
+        <v>50048</v>
+      </c>
+      <c r="C52" t="s">
+        <v>104</v>
+      </c>
+      <c r="D52" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="1:4">
+      <c r="A53" s="1">
+        <v>150048</v>
+      </c>
+      <c r="B53" s="1">
+        <v>50049</v>
+      </c>
+      <c r="C53" t="s">
+        <v>106</v>
+      </c>
+      <c r="D53" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:4">
+      <c r="A54" s="1">
+        <v>150049</v>
+      </c>
+      <c r="B54" s="1">
+        <v>50050</v>
+      </c>
+      <c r="C54" t="s">
+        <v>108</v>
+      </c>
+      <c r="D54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:4">
+      <c r="A55" s="1">
+        <v>150050</v>
+      </c>
+      <c r="B55" s="1">
+        <v>50051</v>
+      </c>
+      <c r="C55" t="s">
+        <v>110</v>
+      </c>
+      <c r="D55" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:4">
+      <c r="A56" s="1">
+        <v>150051</v>
+      </c>
+      <c r="B56" s="1">
+        <v>50052</v>
+      </c>
+      <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:4">
+      <c r="A57" s="1">
+        <v>150052</v>
+      </c>
+      <c r="B57" s="1">
+        <v>50053</v>
+      </c>
+      <c r="C57" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:4">
+      <c r="A58" s="1">
+        <v>150053</v>
+      </c>
+      <c r="B58" s="1">
+        <v>50054</v>
+      </c>
+      <c r="C58" t="s">
+        <v>116</v>
+      </c>
+      <c r="D58" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:4">
+      <c r="A59" s="1">
+        <v>150054</v>
+      </c>
+      <c r="B59" s="1">
+        <v>50055</v>
+      </c>
+      <c r="C59" t="s">
+        <v>118</v>
+      </c>
+      <c r="D59" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:4">
+      <c r="A60" s="1">
+        <v>150055</v>
+      </c>
+      <c r="B60" s="1">
+        <v>50056</v>
+      </c>
+      <c r="C60" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="1:4">
+      <c r="A61" s="1">
+        <v>150056</v>
+      </c>
+      <c r="B61" s="1">
+        <v>50057</v>
+      </c>
+      <c r="C61" t="s">
+        <v>122</v>
+      </c>
+      <c r="D61" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="1:4">
+      <c r="A62" s="1">
+        <v>150057</v>
+      </c>
+      <c r="B62" s="1">
+        <v>50058</v>
+      </c>
+      <c r="C62" t="s">
+        <v>124</v>
+      </c>
+      <c r="D62" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="1:4">
+      <c r="A63" s="1">
+        <v>150058</v>
+      </c>
+      <c r="B63" s="1">
+        <v>50059</v>
+      </c>
+      <c r="C63" t="s">
+        <v>126</v>
+      </c>
+      <c r="D63" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="1:4">
+      <c r="A64" s="1">
+        <v>150059</v>
+      </c>
+      <c r="B64" s="1">
+        <v>50060</v>
+      </c>
+      <c r="C64" t="s">
+        <v>128</v>
+      </c>
+      <c r="D64" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="1:4">
+      <c r="A65" s="1">
+        <v>150060</v>
+      </c>
+      <c r="B65" s="1">
+        <v>50061</v>
+      </c>
+      <c r="C65" t="s">
+        <v>130</v>
+      </c>
+      <c r="D65" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="1:4">
+      <c r="A66" s="1">
+        <v>150061</v>
+      </c>
+      <c r="B66" s="1">
+        <v>50062</v>
+      </c>
+      <c r="C66" t="s">
+        <v>132</v>
+      </c>
+      <c r="D66" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="1:4">
+      <c r="A67" s="1">
+        <v>150062</v>
+      </c>
+      <c r="B67" s="1">
+        <v>50063</v>
+      </c>
+      <c r="C67" t="s">
+        <v>134</v>
+      </c>
+      <c r="D67" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="1:4">
+      <c r="A68" s="1">
+        <v>150063</v>
+      </c>
+      <c r="B68" s="1">
+        <v>50064</v>
+      </c>
+      <c r="C68" t="s">
+        <v>136</v>
+      </c>
+      <c r="D68" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="1:4">
+      <c r="A69" s="1">
+        <v>150064</v>
+      </c>
+      <c r="B69" s="1">
+        <v>50065</v>
+      </c>
+      <c r="C69" t="s">
+        <v>138</v>
+      </c>
+      <c r="D69" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="1:4">
+      <c r="A70" s="1">
+        <v>150065</v>
+      </c>
+      <c r="B70" s="1">
+        <v>50066</v>
+      </c>
+      <c r="C70" t="s">
+        <v>140</v>
+      </c>
+      <c r="D70" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="1:4">
+      <c r="A71" s="1">
+        <v>150066</v>
+      </c>
+      <c r="B71" s="1">
+        <v>50067</v>
+      </c>
+      <c r="C71" t="s">
+        <v>142</v>
+      </c>
+      <c r="D71" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="1:4">
+      <c r="A72" s="1">
+        <v>150067</v>
+      </c>
+      <c r="B72" s="1">
+        <v>50068</v>
+      </c>
+      <c r="C72" t="s">
+        <v>144</v>
+      </c>
+      <c r="D72" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="1:4">
+      <c r="A73" s="1">
+        <v>150068</v>
+      </c>
+      <c r="B73" s="1">
+        <v>50069</v>
+      </c>
+      <c r="C73" t="s">
+        <v>146</v>
+      </c>
+      <c r="D73" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="1:4">
+      <c r="A74" s="1">
+        <v>150069</v>
+      </c>
+      <c r="B74" s="1">
+        <v>50070</v>
+      </c>
+      <c r="C74" t="s">
+        <v>148</v>
+      </c>
+      <c r="D74" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="1:4">
+      <c r="A75" s="1">
+        <v>150070</v>
+      </c>
+      <c r="B75" s="1">
+        <v>50071</v>
+      </c>
+      <c r="C75" t="s">
+        <v>150</v>
+      </c>
+      <c r="D75" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="1:4">
+      <c r="A76" s="1">
+        <v>150071</v>
+      </c>
+      <c r="B76" s="1">
+        <v>50072</v>
+      </c>
+      <c r="C76" t="s">
+        <v>152</v>
+      </c>
+      <c r="D76" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="1:4">
+      <c r="A77">
+        <v>150072</v>
+      </c>
+      <c r="B77">
+        <v>50073</v>
+      </c>
+      <c r="C77" t="s">
+        <v>154</v>
+      </c>
+      <c r="D77" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="1:4">
+      <c r="A78">
+        <v>150073</v>
+      </c>
+      <c r="B78">
+        <v>50074</v>
+      </c>
+      <c r="C78" t="s">
+        <v>156</v>
+      </c>
+      <c r="D78" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="1:4">
+      <c r="A79">
+        <v>150074</v>
+      </c>
+      <c r="B79">
+        <v>50075</v>
+      </c>
+      <c r="C79" t="s">
+        <v>158</v>
+      </c>
+      <c r="D79" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:4">
+      <c r="A80">
+        <v>150075</v>
+      </c>
+      <c r="B80">
+        <v>50076</v>
+      </c>
+      <c r="C80" t="s">
+        <v>160</v>
+      </c>
+      <c r="D80" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="1:4">
+      <c r="A81">
+        <v>150076</v>
+      </c>
+      <c r="B81">
+        <v>50077</v>
+      </c>
+      <c r="C81" t="s">
+        <v>162</v>
+      </c>
+      <c r="D81" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="1:4">
+      <c r="A82">
+        <v>150077</v>
+      </c>
+      <c r="B82">
+        <v>50078</v>
+      </c>
+      <c r="C82" t="s">
+        <v>164</v>
+      </c>
+      <c r="D82" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="1:4">
+      <c r="A83">
+        <v>150078</v>
+      </c>
+      <c r="B83">
+        <v>50079</v>
+      </c>
+      <c r="C83" t="s">
+        <v>166</v>
+      </c>
+      <c r="D83" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="1:4">
+      <c r="A84">
+        <v>150079</v>
+      </c>
+      <c r="B84">
+        <v>50080</v>
+      </c>
+      <c r="C84" t="s">
+        <v>168</v>
+      </c>
+      <c r="D84" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="1:4">
+      <c r="A85">
+        <v>150080</v>
+      </c>
+      <c r="B85">
+        <v>50081</v>
+      </c>
+      <c r="C85" t="s">
+        <v>170</v>
+      </c>
+      <c r="D85" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="1:4">
+      <c r="A86">
+        <v>150081</v>
+      </c>
+      <c r="B86">
+        <v>50082</v>
+      </c>
+      <c r="C86" t="s">
+        <v>172</v>
+      </c>
+      <c r="D86" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="1:4">
+      <c r="A87">
+        <v>150082</v>
+      </c>
+      <c r="B87">
+        <v>50083</v>
+      </c>
+      <c r="C87" t="s">
+        <v>174</v>
+      </c>
+      <c r="D87" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="1:4">
+      <c r="A88">
+        <v>150083</v>
+      </c>
+      <c r="B88">
+        <v>50084</v>
+      </c>
+      <c r="C88" t="s">
+        <v>176</v>
+      </c>
+      <c r="D88" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="1:4">
+      <c r="A89">
+        <v>150084</v>
+      </c>
+      <c r="B89">
+        <v>50085</v>
+      </c>
+      <c r="C89" t="s">
+        <v>178</v>
+      </c>
+      <c r="D89" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="1:4">
+      <c r="A90">
+        <v>150085</v>
+      </c>
+      <c r="B90">
+        <v>50086</v>
+      </c>
+      <c r="C90" t="s">
+        <v>180</v>
+      </c>
+      <c r="D90" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="1:4">
+      <c r="A91">
+        <v>150086</v>
+      </c>
+      <c r="B91">
+        <v>50087</v>
+      </c>
+      <c r="C91" t="s">
+        <v>182</v>
+      </c>
+      <c r="D91" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="1:4">
+      <c r="A92">
+        <v>150087</v>
+      </c>
+      <c r="B92">
+        <v>50088</v>
+      </c>
+      <c r="C92" t="s">
+        <v>184</v>
+      </c>
+      <c r="D92" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="1:4">
+      <c r="A93">
+        <v>150088</v>
+      </c>
+      <c r="B93">
+        <v>50089</v>
+      </c>
+      <c r="C93" t="s">
+        <v>186</v>
+      </c>
+      <c r="D93" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="1:4">
+      <c r="A94">
+        <v>150089</v>
+      </c>
+      <c r="B94">
+        <v>50090</v>
+      </c>
+      <c r="C94" t="s">
+        <v>188</v>
+      </c>
+      <c r="D94" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="1:4">
+      <c r="A95">
+        <v>150090</v>
+      </c>
+      <c r="B95">
+        <v>50091</v>
+      </c>
+      <c r="C95" t="s">
+        <v>190</v>
+      </c>
+      <c r="D95" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="1:4">
+      <c r="A96">
+        <v>150091</v>
+      </c>
+      <c r="B96">
+        <v>50092</v>
+      </c>
+      <c r="C96" t="s">
+        <v>192</v>
+      </c>
+      <c r="D96" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="1:4">
+      <c r="A97">
+        <v>150092</v>
+      </c>
+      <c r="B97">
+        <v>50093</v>
+      </c>
+      <c r="C97" t="s">
+        <v>194</v>
+      </c>
+      <c r="D97" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="1:4">
+      <c r="A98">
+        <v>150093</v>
+      </c>
+      <c r="B98">
+        <v>50094</v>
+      </c>
+      <c r="C98" t="s">
+        <v>196</v>
+      </c>
+      <c r="D98" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="1:4">
+      <c r="A99">
+        <v>150094</v>
+      </c>
+      <c r="B99">
+        <v>50095</v>
+      </c>
+      <c r="C99" t="s">
+        <v>198</v>
+      </c>
+      <c r="D99" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="1:4">
+      <c r="A100">
+        <v>150095</v>
+      </c>
+      <c r="B100">
+        <v>50096</v>
+      </c>
+      <c r="C100" t="s">
+        <v>200</v>
+      </c>
+      <c r="D100" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="1:4">
+      <c r="A101">
+        <v>150096</v>
+      </c>
+      <c r="B101">
+        <v>50097</v>
+      </c>
+      <c r="C101" t="s">
+        <v>202</v>
+      </c>
+      <c r="D101" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="1:4">
+      <c r="A102">
+        <v>150097</v>
+      </c>
+      <c r="B102">
+        <v>50098</v>
+      </c>
+      <c r="C102" t="s">
+        <v>204</v>
+      </c>
+      <c r="D102" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="1:4">
+      <c r="A103">
+        <v>150098</v>
+      </c>
+      <c r="B103">
+        <v>50099</v>
+      </c>
+      <c r="C103" t="s">
+        <v>206</v>
+      </c>
+      <c r="D103" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="1:4">
+      <c r="A104">
+        <v>150099</v>
+      </c>
+      <c r="B104">
+        <v>50100</v>
+      </c>
+      <c r="C104" t="s">
+        <v>208</v>
+      </c>
+      <c r="D104" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="1:4">
+      <c r="A105">
+        <v>150100</v>
+      </c>
+      <c r="B105">
+        <v>50101</v>
+      </c>
+      <c r="C105" t="s">
+        <v>210</v>
+      </c>
+      <c r="D105" t="s">
+        <v>211</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
